--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/100000/Output_22_38.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/100000/Output_22_38.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1601951.990934462</v>
+        <v>1596276.594385568</v>
       </c>
     </row>
     <row r="7">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11300478.83142333</v>
+        <v>11333548.73828869</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6325411.39193041</v>
+        <v>6321476.934567056</v>
       </c>
     </row>
     <row r="11">
@@ -23215,28 +23215,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>360.7338416634806</v>
+        <v>354.2324922389901</v>
       </c>
       <c r="C11" t="n">
-        <v>343.2728917710076</v>
+        <v>336.771542346517</v>
       </c>
       <c r="D11" t="n">
-        <v>332.683041620683</v>
+        <v>326.1816921961924</v>
       </c>
       <c r="E11" t="n">
-        <v>359.9303700722618</v>
+        <v>353.4290206477713</v>
       </c>
       <c r="F11" t="n">
-        <v>384.8760457417114</v>
+        <v>378.3746963172209</v>
       </c>
       <c r="G11" t="n">
-        <v>393.302737515135</v>
+        <v>386.8013880906445</v>
       </c>
       <c r="H11" t="n">
-        <v>317.4748021157671</v>
+        <v>310.9734526912766</v>
       </c>
       <c r="I11" t="n">
-        <v>188.4758895704059</v>
+        <v>181.9745401459154</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -23263,28 +23263,28 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>127.8691179411497</v>
+        <v>121.3677685166592</v>
       </c>
       <c r="S11" t="n">
-        <v>187.0200695862453</v>
+        <v>180.5187201617549</v>
       </c>
       <c r="T11" t="n">
-        <v>201.0958495641314</v>
+        <v>194.5945001396409</v>
       </c>
       <c r="U11" t="n">
-        <v>229.3456529078365</v>
+        <v>222.844303483346</v>
       </c>
       <c r="V11" t="n">
-        <v>305.7522584701349</v>
+        <v>299.2509090456444</v>
       </c>
       <c r="W11" t="n">
-        <v>327.240968717413</v>
+        <v>320.7396192929225</v>
       </c>
       <c r="X11" t="n">
-        <v>347.731100678469</v>
+        <v>341.2297512539785</v>
       </c>
       <c r="Y11" t="n">
-        <v>364.2379386560536</v>
+        <v>357.7365892315631</v>
       </c>
     </row>
     <row r="12">
@@ -23294,28 +23294,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>144.5331836498673</v>
+        <v>138.0318342253769</v>
       </c>
       <c r="C12" t="n">
-        <v>150.7084989883157</v>
+        <v>144.2071495638253</v>
       </c>
       <c r="D12" t="n">
-        <v>125.4450655646388</v>
+        <v>118.9437161401483</v>
       </c>
       <c r="E12" t="n">
-        <v>135.6450804554009</v>
+        <v>129.1437310309105</v>
       </c>
       <c r="F12" t="n">
-        <v>123.0692123933839</v>
+        <v>116.5678629688934</v>
       </c>
       <c r="G12" t="n">
-        <v>115.3435171632106</v>
+        <v>108.8421677387201</v>
       </c>
       <c r="H12" t="n">
-        <v>90.23544423649646</v>
+        <v>83.73409481200596</v>
       </c>
       <c r="I12" t="n">
-        <v>67.39663285141508</v>
+        <v>60.89528342692459</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -23342,28 +23342,28 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>78.15783415264313</v>
+        <v>71.65648472815263</v>
       </c>
       <c r="S12" t="n">
-        <v>149.6831711038378</v>
+        <v>143.1818216793473</v>
       </c>
       <c r="T12" t="n">
-        <v>178.1647286948216</v>
+        <v>171.6633792703311</v>
       </c>
       <c r="U12" t="n">
-        <v>203.9413820809748</v>
+        <v>197.4400326564843</v>
       </c>
       <c r="V12" t="n">
-        <v>210.8005871494253</v>
+        <v>204.2992377249348</v>
       </c>
       <c r="W12" t="n">
-        <v>229.6949831609196</v>
+        <v>223.1936337364291</v>
       </c>
       <c r="X12" t="n">
-        <v>183.7729852034775</v>
+        <v>177.271635778987</v>
       </c>
       <c r="Y12" t="n">
-        <v>183.6826957773044</v>
+        <v>177.1813463528139</v>
       </c>
     </row>
     <row r="13">
@@ -23373,34 +23373,34 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>157.8319801819373</v>
+        <v>151.3306307574468</v>
       </c>
       <c r="C13" t="n">
-        <v>145.2468210986278</v>
+        <v>138.7454716741373</v>
       </c>
       <c r="D13" t="n">
-        <v>126.6154730182124</v>
+        <v>120.1141235937219</v>
       </c>
       <c r="E13" t="n">
-        <v>124.4339626465692</v>
+        <v>117.9326132220787</v>
       </c>
       <c r="F13" t="n">
-        <v>123.4210480229312</v>
+        <v>116.9196985984408</v>
       </c>
       <c r="G13" t="n">
-        <v>145.9909793584588</v>
+        <v>139.4896299339683</v>
       </c>
       <c r="H13" t="n">
-        <v>140.2271725074396</v>
+        <v>133.7258230829491</v>
       </c>
       <c r="I13" t="n">
-        <v>133.4504749272583</v>
+        <v>126.9491255027678</v>
       </c>
       <c r="J13" t="n">
-        <v>71.35918011667277</v>
+        <v>64.85783069218229</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2694918258823407</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -23418,31 +23418,31 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>64.16204325169439</v>
+        <v>57.66069382720389</v>
       </c>
       <c r="R13" t="n">
-        <v>155.2933913771695</v>
+        <v>148.792041952679</v>
       </c>
       <c r="S13" t="n">
-        <v>202.0165980369723</v>
+        <v>195.5152486124818</v>
       </c>
       <c r="T13" t="n">
-        <v>205.9455894282815</v>
+        <v>199.444240003791</v>
       </c>
       <c r="U13" t="n">
-        <v>264.3190293564909</v>
+        <v>257.8176799320004</v>
       </c>
       <c r="V13" t="n">
-        <v>230.137643323828</v>
+        <v>223.6362938993375</v>
       </c>
       <c r="W13" t="n">
-        <v>264.522998336591</v>
+        <v>258.0216489121005</v>
       </c>
       <c r="X13" t="n">
-        <v>203.7096553890372</v>
+        <v>197.2083059645467</v>
       </c>
       <c r="Y13" t="n">
-        <v>196.5846533520948</v>
+        <v>190.0833039276043</v>
       </c>
     </row>
     <row r="14">
@@ -23452,28 +23452,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>288.7338416634806</v>
+        <v>289.3746615468078</v>
       </c>
       <c r="C14" t="n">
-        <v>271.2728917710076</v>
+        <v>271.9137116543347</v>
       </c>
       <c r="D14" t="n">
-        <v>260.683041620683</v>
+        <v>261.3238615040102</v>
       </c>
       <c r="E14" t="n">
-        <v>287.9303700722618</v>
+        <v>288.571189955589</v>
       </c>
       <c r="F14" t="n">
-        <v>312.8760457417114</v>
+        <v>313.5168656250387</v>
       </c>
       <c r="G14" t="n">
-        <v>321.302737515135</v>
+        <v>321.9435573984623</v>
       </c>
       <c r="H14" t="n">
-        <v>245.4748021157671</v>
+        <v>246.1156219990944</v>
       </c>
       <c r="I14" t="n">
-        <v>116.4758895704059</v>
+        <v>117.1167094537331</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -23500,28 +23500,28 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>55.86911794114968</v>
+        <v>56.50993782447691</v>
       </c>
       <c r="S14" t="n">
-        <v>115.0200695862453</v>
+        <v>115.6608894695726</v>
       </c>
       <c r="T14" t="n">
-        <v>129.0958495641314</v>
+        <v>129.7366694474586</v>
       </c>
       <c r="U14" t="n">
-        <v>157.3456529078365</v>
+        <v>157.9864727911637</v>
       </c>
       <c r="V14" t="n">
-        <v>233.7522584701349</v>
+        <v>234.3930783534621</v>
       </c>
       <c r="W14" t="n">
-        <v>255.240968717413</v>
+        <v>255.8817886007402</v>
       </c>
       <c r="X14" t="n">
-        <v>275.731100678469</v>
+        <v>276.3719205617963</v>
       </c>
       <c r="Y14" t="n">
-        <v>292.2379386560536</v>
+        <v>292.8787585393808</v>
       </c>
     </row>
     <row r="15">
@@ -23531,25 +23531,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>72.53318364986734</v>
+        <v>73.17400353319456</v>
       </c>
       <c r="C15" t="n">
-        <v>78.70849898831574</v>
+        <v>79.34931887164296</v>
       </c>
       <c r="D15" t="n">
-        <v>53.44506556463875</v>
+        <v>54.08588544796598</v>
       </c>
       <c r="E15" t="n">
-        <v>63.64508045540094</v>
+        <v>64.28590033872817</v>
       </c>
       <c r="F15" t="n">
-        <v>51.06921239338388</v>
+        <v>51.7100322767111</v>
       </c>
       <c r="G15" t="n">
-        <v>43.34351716321063</v>
+        <v>43.98433704653786</v>
       </c>
       <c r="H15" t="n">
-        <v>18.23544423649646</v>
+        <v>18.87626411982369</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -23579,28 +23579,28 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>6.157834152643133</v>
+        <v>6.798654035970358</v>
       </c>
       <c r="S15" t="n">
-        <v>77.68317110383782</v>
+        <v>78.32399098716505</v>
       </c>
       <c r="T15" t="n">
-        <v>106.1647286948216</v>
+        <v>106.8055485781488</v>
       </c>
       <c r="U15" t="n">
-        <v>131.9413820809748</v>
+        <v>132.582201964302</v>
       </c>
       <c r="V15" t="n">
-        <v>138.8005871494253</v>
+        <v>139.4414070327525</v>
       </c>
       <c r="W15" t="n">
-        <v>157.6949831609196</v>
+        <v>158.3358030442468</v>
       </c>
       <c r="X15" t="n">
-        <v>111.7729852034775</v>
+        <v>112.4138050868047</v>
       </c>
       <c r="Y15" t="n">
-        <v>111.6826957773044</v>
+        <v>112.3235156606316</v>
       </c>
     </row>
     <row r="16">
@@ -23610,28 +23610,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>85.8319801819373</v>
+        <v>86.47280006526452</v>
       </c>
       <c r="C16" t="n">
-        <v>73.24682109862783</v>
+        <v>73.88764098195506</v>
       </c>
       <c r="D16" t="n">
-        <v>54.61547301821236</v>
+        <v>55.25629290153958</v>
       </c>
       <c r="E16" t="n">
-        <v>52.43396264656917</v>
+        <v>53.0747825298964</v>
       </c>
       <c r="F16" t="n">
-        <v>51.42104802293125</v>
+        <v>52.06186790625847</v>
       </c>
       <c r="G16" t="n">
-        <v>73.99097935845876</v>
+        <v>74.63179924178598</v>
       </c>
       <c r="H16" t="n">
-        <v>68.22717250743958</v>
+        <v>68.8679923907668</v>
       </c>
       <c r="I16" t="n">
-        <v>61.45047492725828</v>
+        <v>62.09129481058551</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -23658,28 +23658,28 @@
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>83.29339137716948</v>
+        <v>83.93421126049671</v>
       </c>
       <c r="S16" t="n">
-        <v>130.0165980369723</v>
+        <v>130.6574179202995</v>
       </c>
       <c r="T16" t="n">
-        <v>133.9455894282815</v>
+        <v>134.5864093116087</v>
       </c>
       <c r="U16" t="n">
-        <v>192.3190293564909</v>
+        <v>192.9598492398181</v>
       </c>
       <c r="V16" t="n">
-        <v>158.137643323828</v>
+        <v>158.7784632071552</v>
       </c>
       <c r="W16" t="n">
-        <v>192.522998336591</v>
+        <v>193.1638182199182</v>
       </c>
       <c r="X16" t="n">
-        <v>131.7096553890372</v>
+        <v>132.3504752723644</v>
       </c>
       <c r="Y16" t="n">
-        <v>124.5846533520948</v>
+        <v>125.225473235422</v>
       </c>
     </row>
     <row r="17">
@@ -23689,28 +23689,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>288.7338416634806</v>
+        <v>289.3746615468078</v>
       </c>
       <c r="C17" t="n">
-        <v>271.2728917710076</v>
+        <v>271.9137116543347</v>
       </c>
       <c r="D17" t="n">
-        <v>260.683041620683</v>
+        <v>261.3238615040102</v>
       </c>
       <c r="E17" t="n">
-        <v>287.9303700722618</v>
+        <v>288.571189955589</v>
       </c>
       <c r="F17" t="n">
-        <v>312.8760457417114</v>
+        <v>313.5168656250387</v>
       </c>
       <c r="G17" t="n">
-        <v>321.302737515135</v>
+        <v>321.9435573984623</v>
       </c>
       <c r="H17" t="n">
-        <v>245.4748021157671</v>
+        <v>246.1156219990944</v>
       </c>
       <c r="I17" t="n">
-        <v>116.4758895704059</v>
+        <v>117.1167094537331</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -23737,28 +23737,28 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>55.86911794114968</v>
+        <v>56.50993782447691</v>
       </c>
       <c r="S17" t="n">
-        <v>115.0200695862453</v>
+        <v>115.6608894695726</v>
       </c>
       <c r="T17" t="n">
-        <v>129.0958495641314</v>
+        <v>129.7366694474586</v>
       </c>
       <c r="U17" t="n">
-        <v>157.3456529078365</v>
+        <v>157.9864727911637</v>
       </c>
       <c r="V17" t="n">
-        <v>233.7522584701349</v>
+        <v>234.3930783534621</v>
       </c>
       <c r="W17" t="n">
-        <v>255.240968717413</v>
+        <v>255.8817886007402</v>
       </c>
       <c r="X17" t="n">
-        <v>275.731100678469</v>
+        <v>276.3719205617963</v>
       </c>
       <c r="Y17" t="n">
-        <v>292.2379386560536</v>
+        <v>292.8787585393808</v>
       </c>
     </row>
     <row r="18">
@@ -23768,25 +23768,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>72.53318364986734</v>
+        <v>73.17400353319456</v>
       </c>
       <c r="C18" t="n">
-        <v>78.70849898831574</v>
+        <v>79.34931887164296</v>
       </c>
       <c r="D18" t="n">
-        <v>53.44506556463875</v>
+        <v>54.08588544796598</v>
       </c>
       <c r="E18" t="n">
-        <v>63.64508045540094</v>
+        <v>64.28590033872817</v>
       </c>
       <c r="F18" t="n">
-        <v>51.06921239338388</v>
+        <v>51.7100322767111</v>
       </c>
       <c r="G18" t="n">
-        <v>43.34351716321063</v>
+        <v>43.98433704653786</v>
       </c>
       <c r="H18" t="n">
-        <v>18.23544423649646</v>
+        <v>18.87626411982369</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -23816,28 +23816,28 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>6.157834152643133</v>
+        <v>6.798654035970358</v>
       </c>
       <c r="S18" t="n">
-        <v>77.68317110383782</v>
+        <v>78.32399098716505</v>
       </c>
       <c r="T18" t="n">
-        <v>106.1647286948216</v>
+        <v>106.8055485781488</v>
       </c>
       <c r="U18" t="n">
-        <v>131.9413820809748</v>
+        <v>132.582201964302</v>
       </c>
       <c r="V18" t="n">
-        <v>138.8005871494253</v>
+        <v>139.4414070327525</v>
       </c>
       <c r="W18" t="n">
-        <v>157.6949831609196</v>
+        <v>158.3358030442468</v>
       </c>
       <c r="X18" t="n">
-        <v>111.7729852034775</v>
+        <v>112.4138050868047</v>
       </c>
       <c r="Y18" t="n">
-        <v>111.6826957773044</v>
+        <v>112.3235156606316</v>
       </c>
     </row>
     <row r="19">
@@ -23847,28 +23847,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>85.8319801819373</v>
+        <v>86.47280006526452</v>
       </c>
       <c r="C19" t="n">
-        <v>73.24682109862783</v>
+        <v>73.88764098195506</v>
       </c>
       <c r="D19" t="n">
-        <v>54.61547301821236</v>
+        <v>55.25629290153958</v>
       </c>
       <c r="E19" t="n">
-        <v>52.43396264656917</v>
+        <v>53.0747825298964</v>
       </c>
       <c r="F19" t="n">
-        <v>51.42104802293125</v>
+        <v>52.06186790625847</v>
       </c>
       <c r="G19" t="n">
-        <v>73.99097935845876</v>
+        <v>74.63179924178598</v>
       </c>
       <c r="H19" t="n">
-        <v>68.22717250743958</v>
+        <v>68.8679923907668</v>
       </c>
       <c r="I19" t="n">
-        <v>61.45047492725828</v>
+        <v>62.09129481058551</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -23895,28 +23895,28 @@
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>83.29339137716948</v>
+        <v>83.93421126049671</v>
       </c>
       <c r="S19" t="n">
-        <v>130.0165980369723</v>
+        <v>130.6574179202995</v>
       </c>
       <c r="T19" t="n">
-        <v>133.9455894282815</v>
+        <v>134.5864093116087</v>
       </c>
       <c r="U19" t="n">
-        <v>192.3190293564909</v>
+        <v>192.9598492398181</v>
       </c>
       <c r="V19" t="n">
-        <v>158.137643323828</v>
+        <v>158.7784632071552</v>
       </c>
       <c r="W19" t="n">
-        <v>192.522998336591</v>
+        <v>193.1638182199182</v>
       </c>
       <c r="X19" t="n">
-        <v>131.7096553890372</v>
+        <v>132.3504752723644</v>
       </c>
       <c r="Y19" t="n">
-        <v>124.5846533520948</v>
+        <v>125.225473235422</v>
       </c>
     </row>
     <row r="20">
@@ -23926,28 +23926,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>288.7338416634806</v>
+        <v>289.3746615468078</v>
       </c>
       <c r="C20" t="n">
-        <v>271.2728917710076</v>
+        <v>271.9137116543347</v>
       </c>
       <c r="D20" t="n">
-        <v>260.683041620683</v>
+        <v>261.3238615040102</v>
       </c>
       <c r="E20" t="n">
-        <v>287.9303700722618</v>
+        <v>288.571189955589</v>
       </c>
       <c r="F20" t="n">
-        <v>312.8760457417114</v>
+        <v>313.5168656250387</v>
       </c>
       <c r="G20" t="n">
-        <v>321.302737515135</v>
+        <v>321.9435573984623</v>
       </c>
       <c r="H20" t="n">
-        <v>245.4748021157671</v>
+        <v>246.1156219990944</v>
       </c>
       <c r="I20" t="n">
-        <v>116.4758895704059</v>
+        <v>117.1167094537331</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -23974,28 +23974,28 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>55.86911794114968</v>
+        <v>56.50993782447691</v>
       </c>
       <c r="S20" t="n">
-        <v>115.0200695862453</v>
+        <v>115.6608894695726</v>
       </c>
       <c r="T20" t="n">
-        <v>129.0958495641314</v>
+        <v>129.7366694474586</v>
       </c>
       <c r="U20" t="n">
-        <v>157.3456529078365</v>
+        <v>157.9864727911637</v>
       </c>
       <c r="V20" t="n">
-        <v>233.7522584701349</v>
+        <v>234.3930783534621</v>
       </c>
       <c r="W20" t="n">
-        <v>255.240968717413</v>
+        <v>255.8817886007402</v>
       </c>
       <c r="X20" t="n">
-        <v>275.731100678469</v>
+        <v>276.3719205617963</v>
       </c>
       <c r="Y20" t="n">
-        <v>292.2379386560536</v>
+        <v>292.8787585393808</v>
       </c>
     </row>
     <row r="21">
@@ -24005,25 +24005,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>72.53318364986734</v>
+        <v>73.17400353319456</v>
       </c>
       <c r="C21" t="n">
-        <v>78.70849898831574</v>
+        <v>79.34931887164296</v>
       </c>
       <c r="D21" t="n">
-        <v>53.44506556463875</v>
+        <v>54.08588544796598</v>
       </c>
       <c r="E21" t="n">
-        <v>63.64508045540094</v>
+        <v>64.28590033872817</v>
       </c>
       <c r="F21" t="n">
-        <v>51.06921239338388</v>
+        <v>51.7100322767111</v>
       </c>
       <c r="G21" t="n">
-        <v>43.34351716321063</v>
+        <v>43.98433704653786</v>
       </c>
       <c r="H21" t="n">
-        <v>18.23544423649646</v>
+        <v>18.87626411982369</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -24053,28 +24053,28 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>6.157834152643133</v>
+        <v>6.798654035970358</v>
       </c>
       <c r="S21" t="n">
-        <v>77.68317110383782</v>
+        <v>78.32399098716505</v>
       </c>
       <c r="T21" t="n">
-        <v>106.1647286948216</v>
+        <v>106.8055485781488</v>
       </c>
       <c r="U21" t="n">
-        <v>131.9413820809748</v>
+        <v>132.582201964302</v>
       </c>
       <c r="V21" t="n">
-        <v>138.8005871494253</v>
+        <v>139.4414070327525</v>
       </c>
       <c r="W21" t="n">
-        <v>157.6949831609196</v>
+        <v>158.3358030442468</v>
       </c>
       <c r="X21" t="n">
-        <v>111.7729852034775</v>
+        <v>112.4138050868047</v>
       </c>
       <c r="Y21" t="n">
-        <v>111.6826957773044</v>
+        <v>112.3235156606316</v>
       </c>
     </row>
     <row r="22">
@@ -24084,28 +24084,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>85.8319801819373</v>
+        <v>86.47280006526452</v>
       </c>
       <c r="C22" t="n">
-        <v>73.24682109862783</v>
+        <v>73.88764098195506</v>
       </c>
       <c r="D22" t="n">
-        <v>54.61547301821236</v>
+        <v>55.25629290153958</v>
       </c>
       <c r="E22" t="n">
-        <v>52.43396264656917</v>
+        <v>53.0747825298964</v>
       </c>
       <c r="F22" t="n">
-        <v>51.42104802293125</v>
+        <v>52.06186790625847</v>
       </c>
       <c r="G22" t="n">
-        <v>73.99097935845876</v>
+        <v>74.63179924178598</v>
       </c>
       <c r="H22" t="n">
-        <v>68.22717250743958</v>
+        <v>68.8679923907668</v>
       </c>
       <c r="I22" t="n">
-        <v>61.45047492725828</v>
+        <v>62.09129481058551</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -24132,28 +24132,28 @@
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>83.29339137716948</v>
+        <v>83.93421126049671</v>
       </c>
       <c r="S22" t="n">
-        <v>130.0165980369723</v>
+        <v>130.6574179202995</v>
       </c>
       <c r="T22" t="n">
-        <v>133.9455894282815</v>
+        <v>134.5864093116087</v>
       </c>
       <c r="U22" t="n">
-        <v>192.3190293564909</v>
+        <v>192.9598492398181</v>
       </c>
       <c r="V22" t="n">
-        <v>158.137643323828</v>
+        <v>158.7784632071552</v>
       </c>
       <c r="W22" t="n">
-        <v>192.522998336591</v>
+        <v>193.1638182199182</v>
       </c>
       <c r="X22" t="n">
-        <v>131.7096553890372</v>
+        <v>132.3504752723644</v>
       </c>
       <c r="Y22" t="n">
-        <v>124.5846533520948</v>
+        <v>125.225473235422</v>
       </c>
     </row>
     <row r="23">
@@ -24163,28 +24163,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>288.7338416634806</v>
+        <v>289.3746615468078</v>
       </c>
       <c r="C23" t="n">
-        <v>271.2728917710076</v>
+        <v>271.9137116543347</v>
       </c>
       <c r="D23" t="n">
-        <v>260.683041620683</v>
+        <v>261.3238615040102</v>
       </c>
       <c r="E23" t="n">
-        <v>287.9303700722618</v>
+        <v>288.571189955589</v>
       </c>
       <c r="F23" t="n">
-        <v>312.8760457417114</v>
+        <v>313.5168656250387</v>
       </c>
       <c r="G23" t="n">
-        <v>321.302737515135</v>
+        <v>321.9435573984623</v>
       </c>
       <c r="H23" t="n">
-        <v>245.4748021157671</v>
+        <v>246.1156219990944</v>
       </c>
       <c r="I23" t="n">
-        <v>116.4758895704059</v>
+        <v>117.1167094537331</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -24211,28 +24211,28 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>55.86911794114968</v>
+        <v>56.50993782447691</v>
       </c>
       <c r="S23" t="n">
-        <v>115.0200695862453</v>
+        <v>115.6608894695726</v>
       </c>
       <c r="T23" t="n">
-        <v>129.0958495641314</v>
+        <v>129.7366694474586</v>
       </c>
       <c r="U23" t="n">
-        <v>157.3456529078365</v>
+        <v>157.9864727911637</v>
       </c>
       <c r="V23" t="n">
-        <v>233.7522584701349</v>
+        <v>234.3930783534621</v>
       </c>
       <c r="W23" t="n">
-        <v>255.240968717413</v>
+        <v>255.8817886007402</v>
       </c>
       <c r="X23" t="n">
-        <v>275.731100678469</v>
+        <v>276.3719205617963</v>
       </c>
       <c r="Y23" t="n">
-        <v>292.2379386560536</v>
+        <v>292.8787585393808</v>
       </c>
     </row>
     <row r="24">
@@ -24242,25 +24242,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>72.53318364986734</v>
+        <v>73.17400353319456</v>
       </c>
       <c r="C24" t="n">
-        <v>78.70849898831574</v>
+        <v>79.34931887164296</v>
       </c>
       <c r="D24" t="n">
-        <v>53.44506556463875</v>
+        <v>54.08588544796598</v>
       </c>
       <c r="E24" t="n">
-        <v>63.64508045540094</v>
+        <v>64.28590033872817</v>
       </c>
       <c r="F24" t="n">
-        <v>51.06921239338388</v>
+        <v>51.7100322767111</v>
       </c>
       <c r="G24" t="n">
-        <v>43.34351716321063</v>
+        <v>43.98433704653786</v>
       </c>
       <c r="H24" t="n">
-        <v>18.23544423649646</v>
+        <v>18.87626411982369</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -24290,28 +24290,28 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>6.157834152643133</v>
+        <v>6.798654035970358</v>
       </c>
       <c r="S24" t="n">
-        <v>77.68317110383782</v>
+        <v>78.32399098716505</v>
       </c>
       <c r="T24" t="n">
-        <v>106.1647286948216</v>
+        <v>106.8055485781488</v>
       </c>
       <c r="U24" t="n">
-        <v>131.9413820809748</v>
+        <v>132.582201964302</v>
       </c>
       <c r="V24" t="n">
-        <v>138.8005871494253</v>
+        <v>139.4414070327525</v>
       </c>
       <c r="W24" t="n">
-        <v>157.6949831609196</v>
+        <v>158.3358030442468</v>
       </c>
       <c r="X24" t="n">
-        <v>111.7729852034775</v>
+        <v>112.4138050868047</v>
       </c>
       <c r="Y24" t="n">
-        <v>111.6826957773044</v>
+        <v>112.3235156606316</v>
       </c>
     </row>
     <row r="25">
@@ -24321,28 +24321,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>85.8319801819373</v>
+        <v>86.47280006526452</v>
       </c>
       <c r="C25" t="n">
-        <v>73.24682109862783</v>
+        <v>73.88764098195506</v>
       </c>
       <c r="D25" t="n">
-        <v>54.61547301821236</v>
+        <v>55.25629290153958</v>
       </c>
       <c r="E25" t="n">
-        <v>52.43396264656917</v>
+        <v>53.0747825298964</v>
       </c>
       <c r="F25" t="n">
-        <v>51.42104802293125</v>
+        <v>52.06186790625847</v>
       </c>
       <c r="G25" t="n">
-        <v>73.99097935845876</v>
+        <v>74.63179924178598</v>
       </c>
       <c r="H25" t="n">
-        <v>68.22717250743958</v>
+        <v>68.8679923907668</v>
       </c>
       <c r="I25" t="n">
-        <v>61.45047492725828</v>
+        <v>62.09129481058551</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -24369,28 +24369,28 @@
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>83.29339137716948</v>
+        <v>83.93421126049671</v>
       </c>
       <c r="S25" t="n">
-        <v>130.0165980369723</v>
+        <v>130.6574179202995</v>
       </c>
       <c r="T25" t="n">
-        <v>133.9455894282815</v>
+        <v>134.5864093116087</v>
       </c>
       <c r="U25" t="n">
-        <v>192.3190293564909</v>
+        <v>192.9598492398181</v>
       </c>
       <c r="V25" t="n">
-        <v>158.137643323828</v>
+        <v>158.7784632071552</v>
       </c>
       <c r="W25" t="n">
-        <v>192.522998336591</v>
+        <v>193.1638182199182</v>
       </c>
       <c r="X25" t="n">
-        <v>131.7096553890372</v>
+        <v>132.3504752723644</v>
       </c>
       <c r="Y25" t="n">
-        <v>124.5846533520948</v>
+        <v>125.225473235422</v>
       </c>
     </row>
     <row r="26">
@@ -24400,28 +24400,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>293.7338416634806</v>
+        <v>293.3372088120655</v>
       </c>
       <c r="C26" t="n">
-        <v>276.2728917710076</v>
+        <v>275.8762589195925</v>
       </c>
       <c r="D26" t="n">
-        <v>265.683041620683</v>
+        <v>265.2864087692679</v>
       </c>
       <c r="E26" t="n">
-        <v>292.9303700722618</v>
+        <v>292.5337372208467</v>
       </c>
       <c r="F26" t="n">
-        <v>317.8760457417114</v>
+        <v>317.4794128902964</v>
       </c>
       <c r="G26" t="n">
-        <v>326.302737515135</v>
+        <v>325.90610466372</v>
       </c>
       <c r="H26" t="n">
-        <v>250.4748021157671</v>
+        <v>250.0781692643521</v>
       </c>
       <c r="I26" t="n">
-        <v>121.4758895704059</v>
+        <v>121.0792567189908</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -24448,28 +24448,28 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>60.86911794114968</v>
+        <v>60.4724850897346</v>
       </c>
       <c r="S26" t="n">
-        <v>120.0200695862453</v>
+        <v>119.6234367348303</v>
       </c>
       <c r="T26" t="n">
-        <v>134.0958495641314</v>
+        <v>133.6992167127163</v>
       </c>
       <c r="U26" t="n">
-        <v>162.3456529078365</v>
+        <v>161.9490200564214</v>
       </c>
       <c r="V26" t="n">
-        <v>238.7522584701349</v>
+        <v>238.3556256187198</v>
       </c>
       <c r="W26" t="n">
-        <v>260.240968717413</v>
+        <v>259.8443358659979</v>
       </c>
       <c r="X26" t="n">
-        <v>280.731100678469</v>
+        <v>280.334467827054</v>
       </c>
       <c r="Y26" t="n">
-        <v>297.2379386560536</v>
+        <v>296.8413058046385</v>
       </c>
     </row>
     <row r="27">
@@ -24479,28 +24479,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>77.53318364986734</v>
+        <v>77.13655079845226</v>
       </c>
       <c r="C27" t="n">
-        <v>83.70849898831574</v>
+        <v>83.31186613690066</v>
       </c>
       <c r="D27" t="n">
-        <v>58.44506556463875</v>
+        <v>58.04843271322368</v>
       </c>
       <c r="E27" t="n">
-        <v>68.64508045540094</v>
+        <v>68.24844760398587</v>
       </c>
       <c r="F27" t="n">
-        <v>56.06921239338388</v>
+        <v>55.6725795419688</v>
       </c>
       <c r="G27" t="n">
-        <v>48.34351716321063</v>
+        <v>47.94688431179556</v>
       </c>
       <c r="H27" t="n">
-        <v>23.23544423649646</v>
+        <v>22.83881138508139</v>
       </c>
       <c r="I27" t="n">
-        <v>0.396632851415005</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -24527,28 +24527,28 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>11.15783415264313</v>
+        <v>10.76120130122806</v>
       </c>
       <c r="S27" t="n">
-        <v>82.68317110383782</v>
+        <v>82.28653825242274</v>
       </c>
       <c r="T27" t="n">
-        <v>111.1647286948216</v>
+        <v>110.7680958434065</v>
       </c>
       <c r="U27" t="n">
-        <v>136.9413820809748</v>
+        <v>136.5447492295597</v>
       </c>
       <c r="V27" t="n">
-        <v>143.8005871494253</v>
+        <v>143.4039542980102</v>
       </c>
       <c r="W27" t="n">
-        <v>162.6949831609196</v>
+        <v>162.2983503095045</v>
       </c>
       <c r="X27" t="n">
-        <v>116.7729852034775</v>
+        <v>116.3763523520624</v>
       </c>
       <c r="Y27" t="n">
-        <v>116.6826957773044</v>
+        <v>116.2860629258893</v>
       </c>
     </row>
     <row r="28">
@@ -24558,31 +24558,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>90.8319801819373</v>
+        <v>90.43534733052222</v>
       </c>
       <c r="C28" t="n">
-        <v>78.24682109862783</v>
+        <v>77.85018824721276</v>
       </c>
       <c r="D28" t="n">
-        <v>59.61547301821236</v>
+        <v>59.21884016679728</v>
       </c>
       <c r="E28" t="n">
-        <v>57.43396264656917</v>
+        <v>57.03732979515409</v>
       </c>
       <c r="F28" t="n">
-        <v>56.42104802293125</v>
+        <v>56.02441517151617</v>
       </c>
       <c r="G28" t="n">
-        <v>78.99097935845876</v>
+        <v>78.59434650704368</v>
       </c>
       <c r="H28" t="n">
-        <v>73.22717250743958</v>
+        <v>72.8305396560245</v>
       </c>
       <c r="I28" t="n">
-        <v>66.45047492725828</v>
+        <v>66.05384207584321</v>
       </c>
       <c r="J28" t="n">
-        <v>4.359180116672775</v>
+        <v>3.962547265257697</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -24606,28 +24606,28 @@
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>88.29339137716948</v>
+        <v>87.89675852575441</v>
       </c>
       <c r="S28" t="n">
-        <v>135.0165980369723</v>
+        <v>134.6199651855572</v>
       </c>
       <c r="T28" t="n">
-        <v>138.9455894282815</v>
+        <v>138.5489565768664</v>
       </c>
       <c r="U28" t="n">
-        <v>197.3190293564909</v>
+        <v>196.9223965050758</v>
       </c>
       <c r="V28" t="n">
-        <v>163.137643323828</v>
+        <v>162.7410104724129</v>
       </c>
       <c r="W28" t="n">
-        <v>197.522998336591</v>
+        <v>197.1263654851759</v>
       </c>
       <c r="X28" t="n">
-        <v>136.7096553890372</v>
+        <v>136.3130225376221</v>
       </c>
       <c r="Y28" t="n">
-        <v>129.5846533520948</v>
+        <v>129.1880205006797</v>
       </c>
     </row>
     <row r="29">
@@ -24637,28 +24637,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>244.7338416634806</v>
+        <v>245.3903245002699</v>
       </c>
       <c r="C29" t="n">
-        <v>227.2728917710076</v>
+        <v>227.9293746077969</v>
       </c>
       <c r="D29" t="n">
-        <v>216.683041620683</v>
+        <v>217.3395244574723</v>
       </c>
       <c r="E29" t="n">
-        <v>243.9303700722618</v>
+        <v>244.5868529090511</v>
       </c>
       <c r="F29" t="n">
-        <v>268.8760457417114</v>
+        <v>269.5325285785008</v>
       </c>
       <c r="G29" t="n">
-        <v>277.302737515135</v>
+        <v>277.9592203519244</v>
       </c>
       <c r="H29" t="n">
-        <v>201.4748021157671</v>
+        <v>202.1312849525565</v>
       </c>
       <c r="I29" t="n">
-        <v>72.47588957040591</v>
+        <v>73.13237240719528</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -24685,28 +24685,28 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>11.86911794114968</v>
+        <v>12.52560077793905</v>
       </c>
       <c r="S29" t="n">
-        <v>71.02006958624534</v>
+        <v>71.67655242303471</v>
       </c>
       <c r="T29" t="n">
-        <v>85.09584956413136</v>
+        <v>85.75233240092072</v>
       </c>
       <c r="U29" t="n">
-        <v>113.3456529078365</v>
+        <v>114.0021357446259</v>
       </c>
       <c r="V29" t="n">
-        <v>189.7522584701349</v>
+        <v>190.4087413069243</v>
       </c>
       <c r="W29" t="n">
-        <v>211.240968717413</v>
+        <v>211.8974515542024</v>
       </c>
       <c r="X29" t="n">
-        <v>231.731100678469</v>
+        <v>232.3875835152584</v>
       </c>
       <c r="Y29" t="n">
-        <v>248.2379386560536</v>
+        <v>248.894421492843</v>
       </c>
     </row>
     <row r="30">
@@ -24716,19 +24716,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>28.53318364986734</v>
+        <v>29.18966648665671</v>
       </c>
       <c r="C30" t="n">
-        <v>34.70849898831574</v>
+        <v>35.3649818251051</v>
       </c>
       <c r="D30" t="n">
-        <v>9.445065564638753</v>
+        <v>10.10154840142812</v>
       </c>
       <c r="E30" t="n">
-        <v>19.64508045540094</v>
+        <v>20.30156329219031</v>
       </c>
       <c r="F30" t="n">
-        <v>7.069212393383879</v>
+        <v>7.725695230173244</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -24767,25 +24767,25 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>33.68317110383782</v>
+        <v>34.33965394062719</v>
       </c>
       <c r="T30" t="n">
-        <v>62.1647286948216</v>
+        <v>62.82121153161097</v>
       </c>
       <c r="U30" t="n">
-        <v>87.94138208097482</v>
+        <v>88.59786491776418</v>
       </c>
       <c r="V30" t="n">
-        <v>94.80058714942527</v>
+        <v>95.45706998621463</v>
       </c>
       <c r="W30" t="n">
-        <v>113.6949831609196</v>
+        <v>114.351465997709</v>
       </c>
       <c r="X30" t="n">
-        <v>67.77298520347748</v>
+        <v>68.42946804026684</v>
       </c>
       <c r="Y30" t="n">
-        <v>67.68269577730436</v>
+        <v>68.33917861409373</v>
       </c>
     </row>
     <row r="31">
@@ -24795,28 +24795,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>41.8319801819373</v>
+        <v>42.48846301872666</v>
       </c>
       <c r="C31" t="n">
-        <v>29.24682109862783</v>
+        <v>29.9033039354172</v>
       </c>
       <c r="D31" t="n">
-        <v>10.61547301821236</v>
+        <v>11.27195585500172</v>
       </c>
       <c r="E31" t="n">
-        <v>8.433962646569171</v>
+        <v>9.090445483358536</v>
       </c>
       <c r="F31" t="n">
-        <v>7.421048022931245</v>
+        <v>8.077530859720611</v>
       </c>
       <c r="G31" t="n">
-        <v>29.99097935845876</v>
+        <v>30.64746219524812</v>
       </c>
       <c r="H31" t="n">
-        <v>24.22717250743958</v>
+        <v>24.88365534422894</v>
       </c>
       <c r="I31" t="n">
-        <v>17.45047492725828</v>
+        <v>18.10695776404765</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -24843,28 +24843,28 @@
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>39.29339137716948</v>
+        <v>39.94987421395885</v>
       </c>
       <c r="S31" t="n">
-        <v>86.01659803697225</v>
+        <v>86.67308087376162</v>
       </c>
       <c r="T31" t="n">
-        <v>89.94558942828149</v>
+        <v>90.60207226507086</v>
       </c>
       <c r="U31" t="n">
-        <v>148.3190293564909</v>
+        <v>148.9755121932803</v>
       </c>
       <c r="V31" t="n">
-        <v>114.137643323828</v>
+        <v>114.7941261606174</v>
       </c>
       <c r="W31" t="n">
-        <v>148.522998336591</v>
+        <v>149.1794811733804</v>
       </c>
       <c r="X31" t="n">
-        <v>87.70965538903715</v>
+        <v>88.36613822582652</v>
       </c>
       <c r="Y31" t="n">
-        <v>80.58465335209479</v>
+        <v>81.24113618888416</v>
       </c>
     </row>
     <row r="32">
@@ -24874,28 +24874,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>244.7338416634806</v>
+        <v>245.3903245002699</v>
       </c>
       <c r="C32" t="n">
-        <v>227.2728917710076</v>
+        <v>227.9293746077969</v>
       </c>
       <c r="D32" t="n">
-        <v>216.683041620683</v>
+        <v>217.3395244574723</v>
       </c>
       <c r="E32" t="n">
-        <v>243.9303700722618</v>
+        <v>244.5868529090511</v>
       </c>
       <c r="F32" t="n">
-        <v>268.8760457417114</v>
+        <v>269.5325285785008</v>
       </c>
       <c r="G32" t="n">
-        <v>277.302737515135</v>
+        <v>277.9592203519244</v>
       </c>
       <c r="H32" t="n">
-        <v>201.4748021157671</v>
+        <v>202.1312849525565</v>
       </c>
       <c r="I32" t="n">
-        <v>72.47588957040591</v>
+        <v>73.13237240719528</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -24922,28 +24922,28 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>11.86911794114968</v>
+        <v>12.52560077793905</v>
       </c>
       <c r="S32" t="n">
-        <v>71.02006958624534</v>
+        <v>71.67655242303471</v>
       </c>
       <c r="T32" t="n">
-        <v>85.09584956413136</v>
+        <v>85.75233240092072</v>
       </c>
       <c r="U32" t="n">
-        <v>113.3456529078365</v>
+        <v>114.0021357446259</v>
       </c>
       <c r="V32" t="n">
-        <v>189.7522584701349</v>
+        <v>190.4087413069243</v>
       </c>
       <c r="W32" t="n">
-        <v>211.240968717413</v>
+        <v>211.8974515542024</v>
       </c>
       <c r="X32" t="n">
-        <v>231.731100678469</v>
+        <v>232.3875835152584</v>
       </c>
       <c r="Y32" t="n">
-        <v>248.2379386560536</v>
+        <v>248.894421492843</v>
       </c>
     </row>
     <row r="33">
@@ -24953,19 +24953,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>28.53318364986734</v>
+        <v>29.18966648665671</v>
       </c>
       <c r="C33" t="n">
-        <v>34.70849898831574</v>
+        <v>35.3649818251051</v>
       </c>
       <c r="D33" t="n">
-        <v>9.445065564638753</v>
+        <v>10.10154840142812</v>
       </c>
       <c r="E33" t="n">
-        <v>19.64508045540094</v>
+        <v>20.30156329219031</v>
       </c>
       <c r="F33" t="n">
-        <v>7.069212393383879</v>
+        <v>7.725695230173244</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -25004,25 +25004,25 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>33.68317110383782</v>
+        <v>34.33965394062719</v>
       </c>
       <c r="T33" t="n">
-        <v>62.1647286948216</v>
+        <v>62.82121153161097</v>
       </c>
       <c r="U33" t="n">
-        <v>87.94138208097482</v>
+        <v>88.59786491776418</v>
       </c>
       <c r="V33" t="n">
-        <v>94.80058714942527</v>
+        <v>95.45706998621463</v>
       </c>
       <c r="W33" t="n">
-        <v>113.6949831609196</v>
+        <v>114.351465997709</v>
       </c>
       <c r="X33" t="n">
-        <v>67.77298520347748</v>
+        <v>68.42946804026684</v>
       </c>
       <c r="Y33" t="n">
-        <v>67.68269577730436</v>
+        <v>68.33917861409373</v>
       </c>
     </row>
     <row r="34">
@@ -25032,28 +25032,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>41.8319801819373</v>
+        <v>42.48846301872666</v>
       </c>
       <c r="C34" t="n">
-        <v>29.24682109862783</v>
+        <v>29.9033039354172</v>
       </c>
       <c r="D34" t="n">
-        <v>10.61547301821236</v>
+        <v>11.27195585500172</v>
       </c>
       <c r="E34" t="n">
-        <v>8.433962646569171</v>
+        <v>9.090445483358536</v>
       </c>
       <c r="F34" t="n">
-        <v>7.421048022931245</v>
+        <v>8.077530859720611</v>
       </c>
       <c r="G34" t="n">
-        <v>29.99097935845876</v>
+        <v>30.64746219524812</v>
       </c>
       <c r="H34" t="n">
-        <v>24.22717250743958</v>
+        <v>24.88365534422894</v>
       </c>
       <c r="I34" t="n">
-        <v>17.45047492725828</v>
+        <v>18.10695776404765</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -25080,28 +25080,28 @@
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>39.29339137716948</v>
+        <v>39.94987421395885</v>
       </c>
       <c r="S34" t="n">
-        <v>86.01659803697225</v>
+        <v>86.67308087376162</v>
       </c>
       <c r="T34" t="n">
-        <v>89.94558942828149</v>
+        <v>90.60207226507086</v>
       </c>
       <c r="U34" t="n">
-        <v>148.3190293564909</v>
+        <v>148.9755121932803</v>
       </c>
       <c r="V34" t="n">
-        <v>114.137643323828</v>
+        <v>114.7941261606174</v>
       </c>
       <c r="W34" t="n">
-        <v>148.522998336591</v>
+        <v>149.1794811733804</v>
       </c>
       <c r="X34" t="n">
-        <v>87.70965538903715</v>
+        <v>88.36613822582652</v>
       </c>
       <c r="Y34" t="n">
-        <v>80.58465335209479</v>
+        <v>81.24113618888416</v>
       </c>
     </row>
     <row r="35">
@@ -25111,28 +25111,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>244.7338416634806</v>
+        <v>245.3903245002699</v>
       </c>
       <c r="C35" t="n">
-        <v>227.2728917710076</v>
+        <v>227.9293746077969</v>
       </c>
       <c r="D35" t="n">
-        <v>216.683041620683</v>
+        <v>217.3395244574723</v>
       </c>
       <c r="E35" t="n">
-        <v>243.9303700722618</v>
+        <v>244.5868529090511</v>
       </c>
       <c r="F35" t="n">
-        <v>268.8760457417114</v>
+        <v>269.5325285785008</v>
       </c>
       <c r="G35" t="n">
-        <v>277.302737515135</v>
+        <v>277.9592203519244</v>
       </c>
       <c r="H35" t="n">
-        <v>201.4748021157671</v>
+        <v>202.1312849525565</v>
       </c>
       <c r="I35" t="n">
-        <v>72.47588957040591</v>
+        <v>73.13237240719528</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -25159,28 +25159,28 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>11.86911794114968</v>
+        <v>12.52560077793905</v>
       </c>
       <c r="S35" t="n">
-        <v>71.02006958624534</v>
+        <v>71.67655242303471</v>
       </c>
       <c r="T35" t="n">
-        <v>85.09584956413136</v>
+        <v>85.75233240092072</v>
       </c>
       <c r="U35" t="n">
-        <v>113.3456529078365</v>
+        <v>114.0021357446259</v>
       </c>
       <c r="V35" t="n">
-        <v>189.7522584701349</v>
+        <v>190.4087413069243</v>
       </c>
       <c r="W35" t="n">
-        <v>211.240968717413</v>
+        <v>211.8974515542024</v>
       </c>
       <c r="X35" t="n">
-        <v>231.731100678469</v>
+        <v>232.3875835152584</v>
       </c>
       <c r="Y35" t="n">
-        <v>248.2379386560536</v>
+        <v>248.894421492843</v>
       </c>
     </row>
     <row r="36">
@@ -25190,19 +25190,19 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>28.53318364986734</v>
+        <v>29.18966648665671</v>
       </c>
       <c r="C36" t="n">
-        <v>34.70849898831574</v>
+        <v>35.3649818251051</v>
       </c>
       <c r="D36" t="n">
-        <v>9.445065564638753</v>
+        <v>10.10154840142812</v>
       </c>
       <c r="E36" t="n">
-        <v>19.64508045540094</v>
+        <v>20.30156329219031</v>
       </c>
       <c r="F36" t="n">
-        <v>7.069212393383879</v>
+        <v>7.725695230173244</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -25241,25 +25241,25 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>33.68317110383782</v>
+        <v>34.33965394062719</v>
       </c>
       <c r="T36" t="n">
-        <v>62.1647286948216</v>
+        <v>62.82121153161097</v>
       </c>
       <c r="U36" t="n">
-        <v>87.94138208097482</v>
+        <v>88.59786491776418</v>
       </c>
       <c r="V36" t="n">
-        <v>94.80058714942527</v>
+        <v>95.45706998621463</v>
       </c>
       <c r="W36" t="n">
-        <v>113.6949831609196</v>
+        <v>114.351465997709</v>
       </c>
       <c r="X36" t="n">
-        <v>67.77298520347748</v>
+        <v>68.42946804026684</v>
       </c>
       <c r="Y36" t="n">
-        <v>67.68269577730436</v>
+        <v>68.33917861409373</v>
       </c>
     </row>
     <row r="37">
@@ -25269,28 +25269,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>41.8319801819373</v>
+        <v>42.48846301872666</v>
       </c>
       <c r="C37" t="n">
-        <v>29.24682109862783</v>
+        <v>29.9033039354172</v>
       </c>
       <c r="D37" t="n">
-        <v>10.61547301821236</v>
+        <v>11.27195585500172</v>
       </c>
       <c r="E37" t="n">
-        <v>8.433962646569171</v>
+        <v>9.090445483358536</v>
       </c>
       <c r="F37" t="n">
-        <v>7.421048022931245</v>
+        <v>8.077530859720611</v>
       </c>
       <c r="G37" t="n">
-        <v>29.99097935845876</v>
+        <v>30.64746219524812</v>
       </c>
       <c r="H37" t="n">
-        <v>24.22717250743958</v>
+        <v>24.88365534422894</v>
       </c>
       <c r="I37" t="n">
-        <v>17.45047492725828</v>
+        <v>18.10695776404765</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -25317,28 +25317,28 @@
         <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>39.29339137716948</v>
+        <v>39.94987421395885</v>
       </c>
       <c r="S37" t="n">
-        <v>86.01659803697225</v>
+        <v>86.67308087376162</v>
       </c>
       <c r="T37" t="n">
-        <v>89.94558942828149</v>
+        <v>90.60207226507086</v>
       </c>
       <c r="U37" t="n">
-        <v>148.3190293564909</v>
+        <v>148.9755121932803</v>
       </c>
       <c r="V37" t="n">
-        <v>114.137643323828</v>
+        <v>114.7941261606174</v>
       </c>
       <c r="W37" t="n">
-        <v>148.522998336591</v>
+        <v>149.1794811733804</v>
       </c>
       <c r="X37" t="n">
-        <v>87.70965538903715</v>
+        <v>88.36613822582652</v>
       </c>
       <c r="Y37" t="n">
-        <v>80.58465335209479</v>
+        <v>81.24113618888416</v>
       </c>
     </row>
     <row r="38">
@@ -25348,28 +25348,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>244.7338416634806</v>
+        <v>245.3903245002699</v>
       </c>
       <c r="C38" t="n">
-        <v>227.2728917710076</v>
+        <v>227.9293746077969</v>
       </c>
       <c r="D38" t="n">
-        <v>216.683041620683</v>
+        <v>217.3395244574723</v>
       </c>
       <c r="E38" t="n">
-        <v>243.9303700722618</v>
+        <v>244.5868529090511</v>
       </c>
       <c r="F38" t="n">
-        <v>268.8760457417114</v>
+        <v>269.5325285785008</v>
       </c>
       <c r="G38" t="n">
-        <v>277.302737515135</v>
+        <v>277.9592203519244</v>
       </c>
       <c r="H38" t="n">
-        <v>201.4748021157671</v>
+        <v>202.1312849525565</v>
       </c>
       <c r="I38" t="n">
-        <v>72.47588957040591</v>
+        <v>73.13237240719528</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -25396,28 +25396,28 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>11.86911794114968</v>
+        <v>12.52560077793905</v>
       </c>
       <c r="S38" t="n">
-        <v>71.02006958624534</v>
+        <v>71.67655242303471</v>
       </c>
       <c r="T38" t="n">
-        <v>85.09584956413136</v>
+        <v>85.75233240092072</v>
       </c>
       <c r="U38" t="n">
-        <v>113.3456529078365</v>
+        <v>114.0021357446259</v>
       </c>
       <c r="V38" t="n">
-        <v>189.7522584701349</v>
+        <v>190.4087413069243</v>
       </c>
       <c r="W38" t="n">
-        <v>211.240968717413</v>
+        <v>211.8974515542024</v>
       </c>
       <c r="X38" t="n">
-        <v>231.731100678469</v>
+        <v>232.3875835152584</v>
       </c>
       <c r="Y38" t="n">
-        <v>248.2379386560536</v>
+        <v>248.894421492843</v>
       </c>
     </row>
     <row r="39">
@@ -25427,19 +25427,19 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>28.53318364986734</v>
+        <v>29.18966648665671</v>
       </c>
       <c r="C39" t="n">
-        <v>34.70849898831574</v>
+        <v>35.3649818251051</v>
       </c>
       <c r="D39" t="n">
-        <v>9.445065564638753</v>
+        <v>10.10154840142812</v>
       </c>
       <c r="E39" t="n">
-        <v>19.64508045540094</v>
+        <v>20.30156329219031</v>
       </c>
       <c r="F39" t="n">
-        <v>7.069212393383879</v>
+        <v>7.725695230173244</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -25478,25 +25478,25 @@
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>33.68317110383782</v>
+        <v>34.33965394062719</v>
       </c>
       <c r="T39" t="n">
-        <v>62.1647286948216</v>
+        <v>62.82121153161097</v>
       </c>
       <c r="U39" t="n">
-        <v>87.94138208097482</v>
+        <v>88.59786491776418</v>
       </c>
       <c r="V39" t="n">
-        <v>94.80058714942527</v>
+        <v>95.45706998621463</v>
       </c>
       <c r="W39" t="n">
-        <v>113.6949831609196</v>
+        <v>114.351465997709</v>
       </c>
       <c r="X39" t="n">
-        <v>67.77298520347748</v>
+        <v>68.42946804026684</v>
       </c>
       <c r="Y39" t="n">
-        <v>67.68269577730436</v>
+        <v>68.33917861409373</v>
       </c>
     </row>
     <row r="40">
@@ -25506,28 +25506,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>41.8319801819373</v>
+        <v>42.48846301872666</v>
       </c>
       <c r="C40" t="n">
-        <v>29.24682109862783</v>
+        <v>29.9033039354172</v>
       </c>
       <c r="D40" t="n">
-        <v>10.61547301821236</v>
+        <v>11.27195585500172</v>
       </c>
       <c r="E40" t="n">
-        <v>8.433962646569171</v>
+        <v>9.090445483358536</v>
       </c>
       <c r="F40" t="n">
-        <v>7.421048022931245</v>
+        <v>8.077530859720611</v>
       </c>
       <c r="G40" t="n">
-        <v>29.99097935845876</v>
+        <v>30.64746219524812</v>
       </c>
       <c r="H40" t="n">
-        <v>24.22717250743958</v>
+        <v>24.88365534422894</v>
       </c>
       <c r="I40" t="n">
-        <v>17.45047492725828</v>
+        <v>18.10695776404765</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -25554,28 +25554,28 @@
         <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>39.29339137716948</v>
+        <v>39.94987421395885</v>
       </c>
       <c r="S40" t="n">
-        <v>86.01659803697225</v>
+        <v>86.67308087376162</v>
       </c>
       <c r="T40" t="n">
-        <v>89.94558942828149</v>
+        <v>90.60207226507086</v>
       </c>
       <c r="U40" t="n">
-        <v>148.3190293564909</v>
+        <v>148.9755121932803</v>
       </c>
       <c r="V40" t="n">
-        <v>114.137643323828</v>
+        <v>114.7941261606174</v>
       </c>
       <c r="W40" t="n">
-        <v>148.522998336591</v>
+        <v>149.1794811733804</v>
       </c>
       <c r="X40" t="n">
-        <v>87.70965538903715</v>
+        <v>88.36613822582652</v>
       </c>
       <c r="Y40" t="n">
-        <v>80.58465335209479</v>
+        <v>81.24113618888416</v>
       </c>
     </row>
     <row r="41">
@@ -25585,28 +25585,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>261.7338416634806</v>
+        <v>269.9291266595027</v>
       </c>
       <c r="C41" t="n">
-        <v>244.2728917710076</v>
+        <v>252.4681767670297</v>
       </c>
       <c r="D41" t="n">
-        <v>233.683041620683</v>
+        <v>241.8783266167051</v>
       </c>
       <c r="E41" t="n">
-        <v>260.9303700722618</v>
+        <v>269.1256550682839</v>
       </c>
       <c r="F41" t="n">
-        <v>285.8760457417114</v>
+        <v>294.0713307377336</v>
       </c>
       <c r="G41" t="n">
-        <v>294.302737515135</v>
+        <v>302.4980225111572</v>
       </c>
       <c r="H41" t="n">
-        <v>218.4748021157671</v>
+        <v>226.6700871117893</v>
       </c>
       <c r="I41" t="n">
-        <v>89.47588957040591</v>
+        <v>97.67117456642808</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -25633,28 +25633,28 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>28.86911794114968</v>
+        <v>37.06440293717185</v>
       </c>
       <c r="S41" t="n">
-        <v>88.02006958624534</v>
+        <v>96.21535458226751</v>
       </c>
       <c r="T41" t="n">
-        <v>102.0958495641314</v>
+        <v>110.2911345601535</v>
       </c>
       <c r="U41" t="n">
-        <v>130.3456529078365</v>
+        <v>138.5409379038587</v>
       </c>
       <c r="V41" t="n">
-        <v>206.7522584701349</v>
+        <v>214.9475434661571</v>
       </c>
       <c r="W41" t="n">
-        <v>228.240968717413</v>
+        <v>236.4362537134352</v>
       </c>
       <c r="X41" t="n">
-        <v>248.731100678469</v>
+        <v>256.9263856744912</v>
       </c>
       <c r="Y41" t="n">
-        <v>265.2379386560536</v>
+        <v>273.4332236520758</v>
       </c>
     </row>
     <row r="42">
@@ -25664,22 +25664,22 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>45.53318364986734</v>
+        <v>53.72846864588951</v>
       </c>
       <c r="C42" t="n">
-        <v>51.70849898831574</v>
+        <v>59.90378398433791</v>
       </c>
       <c r="D42" t="n">
-        <v>26.44506556463875</v>
+        <v>34.64035056066092</v>
       </c>
       <c r="E42" t="n">
-        <v>36.64508045540094</v>
+        <v>44.84036545142311</v>
       </c>
       <c r="F42" t="n">
-        <v>24.06921239338388</v>
+        <v>32.26449738940605</v>
       </c>
       <c r="G42" t="n">
-        <v>16.34351716321063</v>
+        <v>24.5388021592328</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -25715,25 +25715,25 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>50.68317110383782</v>
+        <v>58.87845609985999</v>
       </c>
       <c r="T42" t="n">
-        <v>79.1647286948216</v>
+        <v>87.36001369084377</v>
       </c>
       <c r="U42" t="n">
-        <v>104.9413820809748</v>
+        <v>113.136667076997</v>
       </c>
       <c r="V42" t="n">
-        <v>111.8005871494253</v>
+        <v>119.9958721454474</v>
       </c>
       <c r="W42" t="n">
-        <v>130.6949831609196</v>
+        <v>138.8902681569418</v>
       </c>
       <c r="X42" t="n">
-        <v>84.77298520347748</v>
+        <v>92.96827019949964</v>
       </c>
       <c r="Y42" t="n">
-        <v>84.68269577730436</v>
+        <v>92.87798077332653</v>
       </c>
     </row>
     <row r="43">
@@ -25743,28 +25743,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>58.8319801819373</v>
+        <v>67.02726517795946</v>
       </c>
       <c r="C43" t="n">
-        <v>46.24682109862783</v>
+        <v>54.44210609465</v>
       </c>
       <c r="D43" t="n">
-        <v>27.61547301821236</v>
+        <v>35.81075801423452</v>
       </c>
       <c r="E43" t="n">
-        <v>25.43396264656917</v>
+        <v>33.62924764259134</v>
       </c>
       <c r="F43" t="n">
-        <v>24.42104802293125</v>
+        <v>32.61633301895341</v>
       </c>
       <c r="G43" t="n">
-        <v>46.99097935845876</v>
+        <v>55.18626435448093</v>
       </c>
       <c r="H43" t="n">
-        <v>41.22717250743958</v>
+        <v>49.42245750346174</v>
       </c>
       <c r="I43" t="n">
-        <v>34.45047492725828</v>
+        <v>42.64575992328045</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -25791,28 +25791,28 @@
         <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>56.29339137716948</v>
+        <v>64.48867637319165</v>
       </c>
       <c r="S43" t="n">
-        <v>103.0165980369723</v>
+        <v>111.2118830329944</v>
       </c>
       <c r="T43" t="n">
-        <v>106.9455894282815</v>
+        <v>115.1408744243037</v>
       </c>
       <c r="U43" t="n">
-        <v>165.3190293564909</v>
+        <v>173.5143143525131</v>
       </c>
       <c r="V43" t="n">
-        <v>131.137643323828</v>
+        <v>139.3329283198502</v>
       </c>
       <c r="W43" t="n">
-        <v>165.522998336591</v>
+        <v>173.7182833326132</v>
       </c>
       <c r="X43" t="n">
-        <v>104.7096553890372</v>
+        <v>112.9049403850593</v>
       </c>
       <c r="Y43" t="n">
-        <v>97.58465335209479</v>
+        <v>105.779938348117</v>
       </c>
     </row>
     <row r="44">
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>334125.5094468902</v>
+        <v>346530.0573123354</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>471130.1449649397</v>
+        <v>469954.3173774202</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>471130.1449649397</v>
+        <v>469954.3173774202</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>471130.1449649397</v>
+        <v>469954.3173774202</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>471130.1449649397</v>
+        <v>469954.3173774202</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>461858.5949203795</v>
+        <v>462607.437743851</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>549685.0570700754</v>
+        <v>548547.2935359791</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>549685.0570700754</v>
+        <v>548547.2935359791</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>549685.0570700754</v>
+        <v>548547.2935359791</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>549685.0570700754</v>
+        <v>548547.2935359791</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>519667.6449678994</v>
+        <v>505186.2485685283</v>
       </c>
     </row>
     <row r="16">
@@ -26261,46 +26261,46 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>778312.5217811863</v>
+        <v>778312.5217811866</v>
       </c>
       <c r="C2" t="n">
-        <v>778312.5217811863</v>
+        <v>778312.5217811865</v>
       </c>
       <c r="D2" t="n">
-        <v>778312.5217811865</v>
+        <v>778312.5217811866</v>
       </c>
       <c r="E2" t="n">
-        <v>256342.4939927301</v>
+        <v>271072.8945829464</v>
       </c>
       <c r="F2" t="n">
-        <v>419035.4986704144</v>
+        <v>417639.2034102341</v>
       </c>
       <c r="G2" t="n">
-        <v>419035.4986704144</v>
+        <v>417639.2034102342</v>
       </c>
       <c r="H2" t="n">
-        <v>419035.4986704145</v>
+        <v>417639.2034102343</v>
       </c>
       <c r="I2" t="n">
-        <v>419035.4986704144</v>
+        <v>417639.2034102341</v>
       </c>
       <c r="J2" t="n">
-        <v>408025.5329924988</v>
+        <v>408914.7838453712</v>
       </c>
       <c r="K2" t="n">
-        <v>512319.4567952629</v>
+        <v>510968.3625985233</v>
       </c>
       <c r="L2" t="n">
-        <v>512319.4567952629</v>
+        <v>510968.3625985231</v>
       </c>
       <c r="M2" t="n">
-        <v>512319.4567952626</v>
+        <v>510968.3625985231</v>
       </c>
       <c r="N2" t="n">
-        <v>512319.4567952629</v>
+        <v>510968.3625985231</v>
       </c>
       <c r="O2" t="n">
-        <v>476673.7799239284</v>
+        <v>459477.1216996758</v>
       </c>
       <c r="P2" t="n">
         <v>204264.0705097481</v>
@@ -26322,10 +26322,10 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>17600</v>
+        <v>22801.07953959239</v>
       </c>
       <c r="F3" t="n">
-        <v>57600</v>
+        <v>51886.26455374583</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -26337,10 +26337,10 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>13600</v>
+        <v>19631.04172738624</v>
       </c>
       <c r="K3" t="n">
-        <v>96800</v>
+        <v>90243.77200318227</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -26365,49 +26365,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>463150.7311021098</v>
+        <v>463844.3331297129</v>
       </c>
       <c r="C4" t="n">
-        <v>463150.7311021098</v>
+        <v>463844.333129713</v>
       </c>
       <c r="D4" t="n">
-        <v>463150.7311021098</v>
+        <v>463844.3331297129</v>
       </c>
       <c r="E4" t="n">
-        <v>149547.2507915203</v>
+        <v>159090.9872052556</v>
       </c>
       <c r="F4" t="n">
-        <v>247294.4197339227</v>
+        <v>247149.1171696497</v>
       </c>
       <c r="G4" t="n">
-        <v>247294.4197339226</v>
+        <v>247149.1171696497</v>
       </c>
       <c r="H4" t="n">
-        <v>247294.4197339227</v>
+        <v>247149.1171696497</v>
       </c>
       <c r="I4" t="n">
-        <v>247294.4197339227</v>
+        <v>247149.1171696497</v>
       </c>
       <c r="J4" t="n">
-        <v>240679.5503527756</v>
+        <v>241907.4209158952</v>
       </c>
       <c r="K4" t="n">
-        <v>303340.1165511275</v>
+        <v>303221.9711224253</v>
       </c>
       <c r="L4" t="n">
-        <v>303340.1165511275</v>
+        <v>303221.9711224253</v>
       </c>
       <c r="M4" t="n">
-        <v>303340.1165511275</v>
+        <v>303221.9711224253</v>
       </c>
       <c r="N4" t="n">
-        <v>303340.1165511275</v>
+        <v>303221.9711224253</v>
       </c>
       <c r="O4" t="n">
-        <v>281923.9283990224</v>
+        <v>272285.6500853598</v>
       </c>
       <c r="P4" t="n">
-        <v>118258.146084591</v>
+        <v>118951.7481121942</v>
       </c>
     </row>
     <row r="5">
@@ -26426,37 +26426,37 @@
         <v>33627.6</v>
       </c>
       <c r="E5" t="n">
-        <v>1849.518</v>
+        <v>2396.079944767491</v>
       </c>
       <c r="F5" t="n">
-        <v>7902.486</v>
+        <v>7848.612913228564</v>
       </c>
       <c r="G5" t="n">
-        <v>7902.486</v>
+        <v>7848.612913228564</v>
       </c>
       <c r="H5" t="n">
-        <v>7902.486</v>
+        <v>7848.612913228564</v>
       </c>
       <c r="I5" t="n">
-        <v>7902.486</v>
+        <v>7848.612913228564</v>
       </c>
       <c r="J5" t="n">
-        <v>7482.141000000001</v>
+        <v>7515.485527185614</v>
       </c>
       <c r="K5" t="n">
-        <v>11601.522</v>
+        <v>11546.33214439395</v>
       </c>
       <c r="L5" t="n">
-        <v>11601.522</v>
+        <v>11546.33214439395</v>
       </c>
       <c r="M5" t="n">
-        <v>11601.522</v>
+        <v>11546.33214439395</v>
       </c>
       <c r="N5" t="n">
-        <v>11601.522</v>
+        <v>11546.33214439395</v>
       </c>
       <c r="O5" t="n">
-        <v>10172.349</v>
+        <v>9483.379585669412</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>281534.1906790766</v>
+        <v>280840.5886514737</v>
       </c>
       <c r="C6" t="n">
-        <v>281534.1906790766</v>
+        <v>280840.5886514735</v>
       </c>
       <c r="D6" t="n">
-        <v>281534.1906790767</v>
+        <v>280840.5886514737</v>
       </c>
       <c r="E6" t="n">
-        <v>87345.72520120976</v>
+        <v>86784.7478933309</v>
       </c>
       <c r="F6" t="n">
-        <v>106238.5929364918</v>
+        <v>110755.2087736099</v>
       </c>
       <c r="G6" t="n">
-        <v>163838.5929364918</v>
+        <v>162641.4733273559</v>
       </c>
       <c r="H6" t="n">
-        <v>163838.5929364918</v>
+        <v>162641.473327356</v>
       </c>
       <c r="I6" t="n">
-        <v>163838.5929364918</v>
+        <v>162641.4733273559</v>
       </c>
       <c r="J6" t="n">
-        <v>146263.8416397232</v>
+        <v>139860.8356749042</v>
       </c>
       <c r="K6" t="n">
-        <v>100577.8182441354</v>
+        <v>105956.2873285218</v>
       </c>
       <c r="L6" t="n">
-        <v>197377.8182441354</v>
+        <v>196200.0593317039</v>
       </c>
       <c r="M6" t="n">
-        <v>197377.8182441351</v>
+        <v>196200.0593317039</v>
       </c>
       <c r="N6" t="n">
-        <v>197377.8182441354</v>
+        <v>196200.0593317039</v>
       </c>
       <c r="O6" t="n">
-        <v>184577.502524906</v>
+        <v>177708.0920286466</v>
       </c>
       <c r="P6" t="n">
-        <v>86005.92442515709</v>
+        <v>85312.32239755394</v>
       </c>
     </row>
   </sheetData>
@@ -26632,37 +26632,37 @@
         <v>400</v>
       </c>
       <c r="E2" t="n">
-        <v>22</v>
+        <v>28.50134942449049</v>
       </c>
       <c r="F2" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G2" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H2" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I2" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J2" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="K2" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="L2" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="M2" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="N2" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="O2" t="n">
-        <v>121</v>
+        <v>112.8047150039778</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -26840,7 +26840,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -26849,40 +26849,40 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>22</v>
+        <v>28.50134942449049</v>
       </c>
       <c r="F2" t="n">
-        <v>72</v>
+        <v>64.85783069218229</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>17</v>
+        <v>24.53880215923279</v>
       </c>
       <c r="K2" t="n">
-        <v>121</v>
+        <v>112.8047150039778</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -26892,7 +26892,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -26916,25 +26916,25 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -26944,16 +26944,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -26968,25 +26968,25 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -27081,10 +27081,10 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>22</v>
+        <v>28.50134942449049</v>
       </c>
       <c r="K2" t="n">
-        <v>72</v>
+        <v>64.85783069218229</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -27096,10 +27096,10 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>17</v>
+        <v>24.53880215923279</v>
       </c>
       <c r="P2" t="n">
-        <v>121</v>
+        <v>112.8047150039778</v>
       </c>
     </row>
     <row r="3">
@@ -28012,28 +28012,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>28.50134942449049</v>
       </c>
       <c r="C11" t="n">
-        <v>22</v>
+        <v>28.50134942449049</v>
       </c>
       <c r="D11" t="n">
-        <v>22</v>
+        <v>28.50134942449049</v>
       </c>
       <c r="E11" t="n">
-        <v>22</v>
+        <v>28.50134942449049</v>
       </c>
       <c r="F11" t="n">
-        <v>22</v>
+        <v>28.50134942449049</v>
       </c>
       <c r="G11" t="n">
-        <v>22</v>
+        <v>28.50134942449049</v>
       </c>
       <c r="H11" t="n">
-        <v>22</v>
+        <v>28.50134942449049</v>
       </c>
       <c r="I11" t="n">
-        <v>22</v>
+        <v>28.50134942449049</v>
       </c>
       <c r="J11" t="n">
         <v>11.94928935461252</v>
@@ -28060,28 +28060,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R11" t="n">
-        <v>22</v>
+        <v>28.50134942449049</v>
       </c>
       <c r="S11" t="n">
-        <v>22</v>
+        <v>28.50134942449049</v>
       </c>
       <c r="T11" t="n">
-        <v>22</v>
+        <v>28.50134942449049</v>
       </c>
       <c r="U11" t="n">
-        <v>22</v>
+        <v>28.50134942449049</v>
       </c>
       <c r="V11" t="n">
-        <v>22</v>
+        <v>28.50134942449049</v>
       </c>
       <c r="W11" t="n">
-        <v>22</v>
+        <v>28.50134942449049</v>
       </c>
       <c r="X11" t="n">
-        <v>22</v>
+        <v>28.50134942449049</v>
       </c>
       <c r="Y11" t="n">
-        <v>22</v>
+        <v>28.50134942449049</v>
       </c>
     </row>
     <row r="12">
@@ -28091,28 +28091,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>22</v>
+        <v>28.50134942449049</v>
       </c>
       <c r="C12" t="n">
-        <v>22</v>
+        <v>28.50134942449049</v>
       </c>
       <c r="D12" t="n">
-        <v>22</v>
+        <v>28.50134942449049</v>
       </c>
       <c r="E12" t="n">
-        <v>22</v>
+        <v>28.50134942449049</v>
       </c>
       <c r="F12" t="n">
-        <v>22</v>
+        <v>28.50134942449049</v>
       </c>
       <c r="G12" t="n">
-        <v>22</v>
+        <v>28.50134942449049</v>
       </c>
       <c r="H12" t="n">
-        <v>22</v>
+        <v>28.50134942449049</v>
       </c>
       <c r="I12" t="n">
-        <v>22</v>
+        <v>28.50134942449049</v>
       </c>
       <c r="J12" t="n">
         <v>0.7465913262578567</v>
@@ -28139,28 +28139,28 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>22</v>
+        <v>28.50134942449049</v>
       </c>
       <c r="S12" t="n">
-        <v>22</v>
+        <v>28.50134942449049</v>
       </c>
       <c r="T12" t="n">
-        <v>22</v>
+        <v>28.50134942449049</v>
       </c>
       <c r="U12" t="n">
-        <v>22</v>
+        <v>28.50134942449049</v>
       </c>
       <c r="V12" t="n">
-        <v>22</v>
+        <v>28.50134942449049</v>
       </c>
       <c r="W12" t="n">
-        <v>22</v>
+        <v>28.50134942449049</v>
       </c>
       <c r="X12" t="n">
-        <v>22</v>
+        <v>28.50134942449049</v>
       </c>
       <c r="Y12" t="n">
-        <v>22</v>
+        <v>28.50134942449049</v>
       </c>
     </row>
     <row r="13">
@@ -28170,34 +28170,34 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>28.50134942449049</v>
       </c>
       <c r="C13" t="n">
-        <v>22</v>
+        <v>28.50134942449049</v>
       </c>
       <c r="D13" t="n">
-        <v>22</v>
+        <v>28.50134942449049</v>
       </c>
       <c r="E13" t="n">
-        <v>22</v>
+        <v>28.50134942449049</v>
       </c>
       <c r="F13" t="n">
-        <v>22</v>
+        <v>28.50134942449049</v>
       </c>
       <c r="G13" t="n">
-        <v>22</v>
+        <v>28.50134942449049</v>
       </c>
       <c r="H13" t="n">
-        <v>22</v>
+        <v>28.50134942449049</v>
       </c>
       <c r="I13" t="n">
-        <v>22</v>
+        <v>28.50134942449049</v>
       </c>
       <c r="J13" t="n">
-        <v>22</v>
+        <v>28.50134942449049</v>
       </c>
       <c r="K13" t="n">
-        <v>22.00000000000051</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -28215,31 +28215,31 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q13" t="n">
-        <v>22</v>
+        <v>28.50134942449049</v>
       </c>
       <c r="R13" t="n">
-        <v>22</v>
+        <v>28.50134942449049</v>
       </c>
       <c r="S13" t="n">
-        <v>22</v>
+        <v>28.50134942449049</v>
       </c>
       <c r="T13" t="n">
-        <v>22</v>
+        <v>28.50134942449049</v>
       </c>
       <c r="U13" t="n">
-        <v>22</v>
+        <v>28.50134942449049</v>
       </c>
       <c r="V13" t="n">
-        <v>22</v>
+        <v>28.50134942449049</v>
       </c>
       <c r="W13" t="n">
-        <v>22</v>
+        <v>28.50134942449049</v>
       </c>
       <c r="X13" t="n">
-        <v>22</v>
+        <v>28.50134942449049</v>
       </c>
       <c r="Y13" t="n">
-        <v>22</v>
+        <v>28.50134942449049</v>
       </c>
     </row>
     <row r="14">
@@ -28249,28 +28249,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J14" t="n">
         <v>11.94928935461252</v>
@@ -28297,28 +28297,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y14" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="15">
@@ -28328,25 +28328,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I15" t="n">
         <v>89.39663285141508</v>
@@ -28376,28 +28376,28 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y15" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="16">
@@ -28407,28 +28407,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J16" t="n">
         <v>93.35918011667277</v>
@@ -28455,28 +28455,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y16" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="17">
@@ -28486,28 +28486,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J17" t="n">
         <v>11.94928935461252</v>
@@ -28534,28 +28534,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y17" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="18">
@@ -28565,25 +28565,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I18" t="n">
         <v>89.39663285141508</v>
@@ -28613,28 +28613,28 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y18" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="19">
@@ -28644,28 +28644,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J19" t="n">
         <v>93.35918011667277</v>
@@ -28692,28 +28692,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y19" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="20">
@@ -28723,28 +28723,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J20" t="n">
         <v>11.94928935461252</v>
@@ -28771,28 +28771,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y20" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="21">
@@ -28802,25 +28802,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I21" t="n">
         <v>89.39663285141508</v>
@@ -28850,28 +28850,28 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y21" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="22">
@@ -28881,28 +28881,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J22" t="n">
         <v>93.35918011667277</v>
@@ -28929,28 +28929,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y22" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="23">
@@ -28960,28 +28960,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J23" t="n">
         <v>11.94928935461252</v>
@@ -29008,28 +29008,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y23" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="24">
@@ -29039,25 +29039,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I24" t="n">
         <v>89.39663285141508</v>
@@ -29087,28 +29087,28 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y24" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="25">
@@ -29118,31 +29118,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="C25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="D25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="E25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="F25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="G25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="H25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="I25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="J25" t="n">
-        <v>93.35918011667286</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K25" t="n">
         <v>22.26949182588285</v>
@@ -29166,28 +29166,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="S25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="T25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="U25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="V25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="W25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="X25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="Y25" t="n">
-        <v>94</v>
+        <v>93.35918011667277</v>
       </c>
     </row>
     <row r="26">
@@ -29197,28 +29197,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="C26" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="D26" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="E26" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="F26" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="G26" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="H26" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="I26" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J26" t="n">
         <v>11.94928935461252</v>
@@ -29245,28 +29245,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R26" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="S26" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="T26" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="U26" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="V26" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="W26" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="X26" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="Y26" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
     </row>
     <row r="27">
@@ -29276,28 +29276,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="C27" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="D27" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="E27" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="F27" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="G27" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="H27" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="I27" t="n">
-        <v>89.00000000000007</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J27" t="n">
         <v>0.7465913262578567</v>
@@ -29324,28 +29324,28 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="S27" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="T27" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="U27" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="V27" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="W27" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="X27" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="Y27" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
     </row>
     <row r="28">
@@ -29355,31 +29355,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="C28" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="D28" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="E28" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="F28" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="G28" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="H28" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="I28" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J28" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="K28" t="n">
         <v>22.26949182588285</v>
@@ -29403,28 +29403,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R28" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="S28" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="T28" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="U28" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="V28" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="W28" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="X28" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="Y28" t="n">
-        <v>89</v>
+        <v>89.39663285141508</v>
       </c>
     </row>
     <row r="29">
@@ -29434,28 +29434,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="C29" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="D29" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="E29" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="F29" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="G29" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H29" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="I29" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="J29" t="n">
         <v>11.94928935461252</v>
@@ -29482,28 +29482,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R29" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="S29" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="T29" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="U29" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="V29" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="W29" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="X29" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Y29" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
     </row>
     <row r="30">
@@ -29513,22 +29513,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="C30" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="D30" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="E30" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="F30" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="G30" t="n">
-        <v>137.3435171632107</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H30" t="n">
         <v>112.2354442364965</v>
@@ -29564,25 +29564,25 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S30" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="T30" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="U30" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="V30" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="W30" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="X30" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Y30" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
     </row>
     <row r="31">
@@ -29592,28 +29592,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="C31" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="D31" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="E31" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="F31" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="G31" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H31" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="I31" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="J31" t="n">
         <v>93.35918011667277</v>
@@ -29640,28 +29640,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R31" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="S31" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="T31" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="U31" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="V31" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="W31" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="X31" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Y31" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
     </row>
     <row r="32">
@@ -29671,28 +29671,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="C32" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="D32" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="E32" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="F32" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="G32" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H32" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="I32" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="J32" t="n">
         <v>11.94928935461252</v>
@@ -29719,28 +29719,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R32" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="S32" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="T32" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="U32" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="V32" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="W32" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="X32" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Y32" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
     </row>
     <row r="33">
@@ -29750,19 +29750,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="C33" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="D33" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="E33" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="F33" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="G33" t="n">
         <v>137.3435171632106</v>
@@ -29801,25 +29801,25 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S33" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="T33" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="U33" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="V33" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="W33" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="X33" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Y33" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
     </row>
     <row r="34">
@@ -29829,28 +29829,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="C34" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="D34" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="E34" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="F34" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="G34" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H34" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="I34" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="J34" t="n">
         <v>93.35918011667277</v>
@@ -29877,28 +29877,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R34" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="S34" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="T34" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="U34" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="V34" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="W34" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="X34" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Y34" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
     </row>
     <row r="35">
@@ -29908,28 +29908,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="C35" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="D35" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="E35" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="F35" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="G35" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H35" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="I35" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="J35" t="n">
         <v>11.94928935461252</v>
@@ -29956,28 +29956,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R35" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="S35" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="T35" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="U35" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="V35" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="W35" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="X35" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Y35" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
     </row>
     <row r="36">
@@ -29987,19 +29987,19 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="C36" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="D36" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="E36" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="F36" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="G36" t="n">
         <v>137.3435171632106</v>
@@ -30038,25 +30038,25 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S36" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="T36" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="U36" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="V36" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="W36" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="X36" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Y36" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
     </row>
     <row r="37">
@@ -30066,28 +30066,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="C37" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="D37" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="E37" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="F37" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="G37" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H37" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="I37" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="J37" t="n">
         <v>93.35918011667277</v>
@@ -30114,28 +30114,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R37" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="S37" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="T37" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="U37" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="V37" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="W37" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="X37" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Y37" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
     </row>
     <row r="38">
@@ -30145,28 +30145,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="C38" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="D38" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="E38" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="F38" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="G38" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H38" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="I38" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="J38" t="n">
         <v>11.94928935461252</v>
@@ -30193,28 +30193,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R38" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="S38" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="T38" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="U38" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="V38" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="W38" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="X38" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Y38" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
     </row>
     <row r="39">
@@ -30224,22 +30224,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="C39" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="D39" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="E39" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="F39" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="G39" t="n">
-        <v>137.3435171632107</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H39" t="n">
         <v>112.2354442364965</v>
@@ -30275,25 +30275,25 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S39" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="T39" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="U39" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="V39" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="W39" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="X39" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Y39" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
     </row>
     <row r="40">
@@ -30303,28 +30303,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="C40" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="D40" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="E40" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="F40" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="G40" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H40" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="I40" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="J40" t="n">
         <v>93.35918011667277</v>
@@ -30351,28 +30351,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R40" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="S40" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="T40" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="U40" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="V40" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="W40" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="X40" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Y40" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
     </row>
     <row r="41">
@@ -30382,28 +30382,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>121</v>
+        <v>112.8047150039778</v>
       </c>
       <c r="C41" t="n">
-        <v>121</v>
+        <v>112.8047150039778</v>
       </c>
       <c r="D41" t="n">
-        <v>121</v>
+        <v>112.8047150039778</v>
       </c>
       <c r="E41" t="n">
-        <v>121</v>
+        <v>112.8047150039778</v>
       </c>
       <c r="F41" t="n">
-        <v>121</v>
+        <v>112.8047150039778</v>
       </c>
       <c r="G41" t="n">
-        <v>121</v>
+        <v>112.8047150039778</v>
       </c>
       <c r="H41" t="n">
-        <v>121</v>
+        <v>112.8047150039778</v>
       </c>
       <c r="I41" t="n">
-        <v>121</v>
+        <v>112.8047150039778</v>
       </c>
       <c r="J41" t="n">
         <v>11.94928935461252</v>
@@ -30430,28 +30430,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R41" t="n">
-        <v>121</v>
+        <v>112.8047150039778</v>
       </c>
       <c r="S41" t="n">
-        <v>121</v>
+        <v>112.8047150039778</v>
       </c>
       <c r="T41" t="n">
-        <v>121</v>
+        <v>112.8047150039778</v>
       </c>
       <c r="U41" t="n">
-        <v>121</v>
+        <v>112.8047150039778</v>
       </c>
       <c r="V41" t="n">
-        <v>121</v>
+        <v>112.8047150039778</v>
       </c>
       <c r="W41" t="n">
-        <v>121</v>
+        <v>112.8047150039778</v>
       </c>
       <c r="X41" t="n">
-        <v>121</v>
+        <v>112.8047150039778</v>
       </c>
       <c r="Y41" t="n">
-        <v>121</v>
+        <v>112.8047150039778</v>
       </c>
     </row>
     <row r="42">
@@ -30461,22 +30461,22 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>121</v>
+        <v>112.8047150039778</v>
       </c>
       <c r="C42" t="n">
-        <v>121</v>
+        <v>112.8047150039778</v>
       </c>
       <c r="D42" t="n">
-        <v>121</v>
+        <v>112.8047150039778</v>
       </c>
       <c r="E42" t="n">
-        <v>121</v>
+        <v>112.8047150039778</v>
       </c>
       <c r="F42" t="n">
-        <v>121</v>
+        <v>112.8047150039778</v>
       </c>
       <c r="G42" t="n">
-        <v>121</v>
+        <v>112.8047150039778</v>
       </c>
       <c r="H42" t="n">
         <v>112.2354442364965</v>
@@ -30512,25 +30512,25 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S42" t="n">
-        <v>121</v>
+        <v>112.8047150039778</v>
       </c>
       <c r="T42" t="n">
-        <v>121</v>
+        <v>112.8047150039778</v>
       </c>
       <c r="U42" t="n">
-        <v>121</v>
+        <v>112.8047150039778</v>
       </c>
       <c r="V42" t="n">
-        <v>121</v>
+        <v>112.8047150039778</v>
       </c>
       <c r="W42" t="n">
-        <v>121</v>
+        <v>112.8047150039778</v>
       </c>
       <c r="X42" t="n">
-        <v>121</v>
+        <v>112.8047150039778</v>
       </c>
       <c r="Y42" t="n">
-        <v>121</v>
+        <v>112.8047150039778</v>
       </c>
     </row>
     <row r="43">
@@ -30540,28 +30540,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>121</v>
+        <v>112.8047150039778</v>
       </c>
       <c r="C43" t="n">
-        <v>121</v>
+        <v>112.8047150039778</v>
       </c>
       <c r="D43" t="n">
-        <v>121</v>
+        <v>112.8047150039778</v>
       </c>
       <c r="E43" t="n">
-        <v>121</v>
+        <v>112.8047150039778</v>
       </c>
       <c r="F43" t="n">
-        <v>121</v>
+        <v>112.8047150039778</v>
       </c>
       <c r="G43" t="n">
-        <v>121</v>
+        <v>112.8047150039778</v>
       </c>
       <c r="H43" t="n">
-        <v>121</v>
+        <v>112.8047150039778</v>
       </c>
       <c r="I43" t="n">
-        <v>121</v>
+        <v>112.8047150039778</v>
       </c>
       <c r="J43" t="n">
         <v>93.35918011667277</v>
@@ -30588,28 +30588,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R43" t="n">
-        <v>121</v>
+        <v>112.8047150039778</v>
       </c>
       <c r="S43" t="n">
-        <v>121</v>
+        <v>112.8047150039778</v>
       </c>
       <c r="T43" t="n">
-        <v>121</v>
+        <v>112.8047150039778</v>
       </c>
       <c r="U43" t="n">
-        <v>121</v>
+        <v>112.8047150039778</v>
       </c>
       <c r="V43" t="n">
-        <v>121</v>
+        <v>112.8047150039778</v>
       </c>
       <c r="W43" t="n">
-        <v>121</v>
+        <v>112.8047150039778</v>
       </c>
       <c r="X43" t="n">
-        <v>121</v>
+        <v>112.8047150039778</v>
       </c>
       <c r="Y43" t="n">
-        <v>121</v>
+        <v>112.8047150039778</v>
       </c>
     </row>
     <row r="44">
